--- a/results/682_z23/2_canaliculi/682_z23_canaliculi_results.xlsx
+++ b/results/682_z23/2_canaliculi/682_z23_canaliculi_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,6 +682,441 @@
         </is>
       </c>
       <c r="G11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>221.5717</v>
+      </c>
+      <c r="D12" t="n">
+        <v>210.2437</v>
+      </c>
+      <c r="E12" t="n">
+        <v>51.1926</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8909.8182</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8646</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1432.672</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>22488.8182</v>
+      </c>
+      <c r="D14" t="n">
+        <v>22056</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3166.3021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03201806</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03067243</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.00806864</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0356529</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.03432295</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.00603288</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3.0793</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.8652</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7844</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>per 100 px</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>213.2727</v>
+      </c>
+      <c r="D20" t="n">
+        <v>215</v>
+      </c>
+      <c r="E20" t="n">
+        <v>77.22839999999999</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>419.4545</v>
+      </c>
+      <c r="D21" t="n">
+        <v>444</v>
+      </c>
+      <c r="E21" t="n">
+        <v>153.0728</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>315.3412</v>
+      </c>
+      <c r="D22" t="n">
+        <v>341.3503</v>
+      </c>
+      <c r="E22" t="n">
+        <v>74.1913</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>890.9974</v>
+      </c>
+      <c r="D23" t="n">
+        <v>845.4651</v>
+      </c>
+      <c r="E23" t="n">
+        <v>145.1624</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>7.4545</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.0671</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10.8182</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.316</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" t="n">
+        <v>13</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.8284</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>11</v>
       </c>
     </row>
@@ -696,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +1353,63 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>field_length_density_w_per_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.04303411</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>field_density_without_flagged_per_px</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0380563</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>field_density_in_roi_per_px</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
         </is>
       </c>
     </row>
@@ -932,7 +1424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +1468,81 @@
           <t>mean_edge_length_px</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1001,6 +1568,51 @@
       </c>
       <c r="H2" t="n">
         <v>19.8044</v>
+      </c>
+      <c r="I2" t="n">
+        <v>105.1543</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3701</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10161</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.03674683</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.03720106</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.8039</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>118</v>
+      </c>
+      <c r="R2" t="n">
+        <v>260</v>
+      </c>
+      <c r="S2" t="n">
+        <v>148.5685</v>
+      </c>
+      <c r="T2" t="n">
+        <v>409.9066</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1028,6 +1640,51 @@
       <c r="H3" t="n">
         <v>8.1213</v>
       </c>
+      <c r="I3" t="n">
+        <v>132.8467</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3699</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7686</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5656</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.01108408</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.02224824</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.5055</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>28</v>
+      </c>
+      <c r="R3" t="n">
+        <v>28</v>
+      </c>
+      <c r="S3" t="n">
+        <v>39.3137</v>
+      </c>
+      <c r="T3" t="n">
+        <v>170.4975</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1054,6 +1711,51 @@
       <c r="H4" t="n">
         <v>30.9994</v>
       </c>
+      <c r="I4" t="n">
+        <v>219.6812</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8976</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20715</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.9689</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.03275401</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03432295</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.276</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>108</v>
+      </c>
+      <c r="R4" t="n">
+        <v>220</v>
+      </c>
+      <c r="S4" t="n">
+        <v>312.066</v>
+      </c>
+      <c r="T4" t="n">
+        <v>768.7716</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W4" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1782,51 @@
       <c r="H5" t="n">
         <v>26.7007</v>
       </c>
+      <c r="I5" t="n">
+        <v>210.2437</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8511</v>
+      </c>
+      <c r="K5" t="n">
+        <v>22591</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.03853836</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.03899783</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.8051</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>274</v>
+      </c>
+      <c r="R5" t="n">
+        <v>562</v>
+      </c>
+      <c r="S5" t="n">
+        <v>374.1615</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1004.0042</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10</v>
+      </c>
+      <c r="V5" t="n">
+        <v>10</v>
+      </c>
+      <c r="W5" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1106,6 +1853,51 @@
       <c r="H6" t="n">
         <v>23.509</v>
       </c>
+      <c r="I6" t="n">
+        <v>335.4214</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12178</v>
+      </c>
+      <c r="K6" t="n">
+        <v>29932</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02767285</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.02943338</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.6832</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>246</v>
+      </c>
+      <c r="R6" t="n">
+        <v>444</v>
+      </c>
+      <c r="S6" t="n">
+        <v>367.8356</v>
+      </c>
+      <c r="T6" t="n">
+        <v>971.5656</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>14</v>
+      </c>
+      <c r="W6" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1132,6 +1924,51 @@
       <c r="H7" t="n">
         <v>36.0179</v>
       </c>
+      <c r="I7" t="n">
+        <v>167.2376</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7485</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20582</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.02765531</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.03648819</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.9898</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>133</v>
+      </c>
+      <c r="R7" t="n">
+        <v>163</v>
+      </c>
+      <c r="S7" t="n">
+        <v>227.4802</v>
+      </c>
+      <c r="T7" t="n">
+        <v>845.4651</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1158,6 +1995,51 @@
       <c r="H8" t="n">
         <v>31.9402</v>
       </c>
+      <c r="I8" t="n">
+        <v>243.5219</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9472</v>
+      </c>
+      <c r="K8" t="n">
+        <v>22056</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03230574</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.033823</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.2851</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>262</v>
+      </c>
+      <c r="R8" t="n">
+        <v>447</v>
+      </c>
+      <c r="S8" t="n">
+        <v>341.3503</v>
+      </c>
+      <c r="T8" t="n">
+        <v>828.5118</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>10</v>
+      </c>
+      <c r="W8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1184,6 +2066,51 @@
       <c r="H9" t="n">
         <v>30.589</v>
       </c>
+      <c r="I9" t="n">
+        <v>167.9239</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7349</v>
+      </c>
+      <c r="K9" t="n">
+        <v>17555</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.05170772</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.04841925</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.7641</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>327</v>
+      </c>
+      <c r="R9" t="n">
+        <v>610</v>
+      </c>
+      <c r="S9" t="n">
+        <v>417.5635</v>
+      </c>
+      <c r="T9" t="n">
+        <v>934.997</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13</v>
+      </c>
+      <c r="W9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1210,6 +2137,51 @@
       <c r="H10" t="n">
         <v>29.5619</v>
       </c>
+      <c r="I10" t="n">
+        <v>282.8944</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8678</v>
+      </c>
+      <c r="K10" t="n">
+        <v>19332</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.7462</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.02996082</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.03445065</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.1209</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>181</v>
+      </c>
+      <c r="R10" t="n">
+        <v>338</v>
+      </c>
+      <c r="S10" t="n">
+        <v>288.2082</v>
+      </c>
+      <c r="T10" t="n">
+        <v>743.8843000000001</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W10" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1236,6 +2208,51 @@
       <c r="H11" t="n">
         <v>31.7551</v>
       </c>
+      <c r="I11" t="n">
+        <v>263.4802</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10172</v>
+      </c>
+      <c r="K11" t="n">
+        <v>24552</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.03067243</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.04268491</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.2772</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>191</v>
+      </c>
+      <c r="R11" t="n">
+        <v>491</v>
+      </c>
+      <c r="S11" t="n">
+        <v>348.4214</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1173.6905</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>14</v>
+      </c>
+      <c r="W11" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1261,6 +2278,51 @@
       </c>
       <c r="H12" t="n">
         <v>37.387</v>
+      </c>
+      <c r="I12" t="n">
+        <v>174.5097</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7570</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20770</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.02562748</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0272027</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.8652</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>144</v>
+      </c>
+      <c r="R12" t="n">
+        <v>297</v>
+      </c>
+      <c r="S12" t="n">
+        <v>216.5807</v>
+      </c>
+      <c r="T12" t="n">
+        <v>647.5412</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1288,6 +2350,51 @@
       <c r="H13" t="n">
         <v>49.3829</v>
       </c>
+      <c r="I13" t="n">
+        <v>210.1665</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8646</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22189</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.02960907</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.03339493</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.3791</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>215</v>
+      </c>
+      <c r="R13" t="n">
+        <v>400</v>
+      </c>
+      <c r="S13" t="n">
+        <v>295.9777</v>
+      </c>
+      <c r="T13" t="n">
+        <v>833.2813</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" t="n">
+        <v>10</v>
+      </c>
+      <c r="W13" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1314,6 +2421,51 @@
       <c r="H14" t="n">
         <v>25.2238</v>
       </c>
+      <c r="I14" t="n">
+        <v>185.8234</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7980</v>
+      </c>
+      <c r="K14" t="n">
+        <v>21610</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.02080201</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.03128181</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.6907</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>132</v>
+      </c>
+      <c r="R14" t="n">
+        <v>348</v>
+      </c>
+      <c r="S14" t="n">
+        <v>192.1665</v>
+      </c>
+      <c r="T14" t="n">
+        <v>782.4945</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1339,6 +2491,51 @@
       </c>
       <c r="H15" t="n">
         <v>36.5639</v>
+      </c>
+      <c r="I15" t="n">
+        <v>259.2792</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9669</v>
+      </c>
+      <c r="K15" t="n">
+        <v>24825</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.03485366</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.03613293</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.8568</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>314</v>
+      </c>
+      <c r="R15" t="n">
+        <v>632</v>
+      </c>
+      <c r="S15" t="n">
+        <v>375.1493</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1010.6488</v>
+      </c>
+      <c r="U15" t="n">
+        <v>11</v>
+      </c>
+      <c r="V15" t="n">
+        <v>13</v>
+      </c>
+      <c r="W15" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
